--- a/Europris modell.xlsx
+++ b/Europris modell.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/augusthodt/Desktop/Aksjemodellering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D328450C-9CDA-534A-B581-305A50CE45CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D9E48F-B00F-4C47-BDD4-824BF4AB2803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17220" activeTab="2" xr2:uid="{A1D7EC49-6B45-5A4D-9144-DCA361DB0A7A}"/>
+    <workbookView xWindow="25300" yWindow="500" windowWidth="25900" windowHeight="26740" activeTab="1" xr2:uid="{A1D7EC49-6B45-5A4D-9144-DCA361DB0A7A}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -2124,7 +2124,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="3">
-        <v>85</v>
+        <v>87.6</v>
       </c>
       <c r="C4" s="23" t="s">
         <v>54</v>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="B6" s="5">
         <f>B4*B5</f>
-        <v>14192.35548</v>
+        <v>14626.474588799998</v>
       </c>
       <c r="C6" s="24" t="s">
         <v>56</v>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="B9" s="6">
         <f>B6-B7+B8</f>
-        <v>15819.31148</v>
+        <v>16253.430588799998</v>
       </c>
       <c r="C9" s="24" t="s">
         <v>73</v>
@@ -2964,7 +2964,7 @@
         <v>-1462</v>
       </c>
       <c r="AM9" s="43">
-        <f t="shared" ref="AM8:AM9" si="15">AL9*1.02</f>
+        <f t="shared" ref="AM9" si="15">AL9*1.02</f>
         <v>-1491.24</v>
       </c>
       <c r="AN9" s="24">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="B14" s="4">
         <f>B6/U41</f>
-        <v>3.5727488759288799</v>
+        <v>3.6820329591925867</v>
       </c>
       <c r="C14" s="24" t="s">
         <v>78</v>
@@ -5367,7 +5367,7 @@
       </c>
       <c r="AY24" s="25">
         <f>(AY23-B4)/B4</f>
-        <v>0.37335029950048876</v>
+        <v>0.33258876093083967</v>
       </c>
     </row>
     <row r="25" spans="2:51" s="24" customFormat="1" x14ac:dyDescent="0.25">
@@ -13332,6 +13332,11 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="AC14 AA12:AB12 AA14:AB14 AA16:AC16 AA18:AB18 AC18 Y14 Y16 Y12:Z13 Y17:Z19 Z16 Y15:Z15 Z14 AD26:AE29 Y26:AC29 AG26:AJ29 AH30:AJ32 AF18 AF12 AF14 AF16 AD18 AD16 AD14 AD8:AK11 AD15:AK15 AE14 AD17:AK17 AE16 AE18 AG16:AK16 AG14:AK14 AD13:AK13 AD12:AE12 AG12:AK12 AG18:AK18" evalError="1"/>
+    <ignoredError sqref="V28 V30:X32 AF30:AF32 V14:V16" formula="1"/>
+    <ignoredError sqref="AD30:AE32 Y30:AC32 AG30:AG32" evalError="1" formula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -13385,18 +13390,18 @@
         <v>52</v>
       </c>
       <c r="C7" s="35">
-        <v>2300</v>
+        <v>2278</v>
       </c>
       <c r="D7" s="34">
         <v>7</v>
       </c>
       <c r="E7" s="35">
         <f>C7*D7</f>
-        <v>16100</v>
+        <v>15946</v>
       </c>
       <c r="F7" s="36">
         <f>E7/Modell!$B$5</f>
-        <v>96.42514957636898</v>
+        <v>95.502822058681986</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -13424,16 +13429,16 @@
       </c>
       <c r="C9" s="37">
         <f>SUM(C7:C8)</f>
-        <v>2662</v>
+        <v>2640</v>
       </c>
       <c r="D9" s="33"/>
       <c r="E9" s="37">
         <f>SUM(E7:E8)</f>
-        <v>17910</v>
+        <v>17756</v>
       </c>
       <c r="F9" s="38">
         <f>E9/Modell!$B$5</f>
-        <v>107.26549247905395</v>
+        <v>106.34316496136694</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -13488,11 +13493,11 @@
       <c r="D14" s="33"/>
       <c r="E14" s="37">
         <f>SUM(E9:E12)</f>
-        <v>16283.044</v>
+        <v>16129.044</v>
       </c>
       <c r="F14" s="38">
         <f>SUM(F9:F12)</f>
-        <v>97.521425668235878</v>
+        <v>96.599098150548869</v>
       </c>
     </row>
   </sheetData>
@@ -13528,15 +13533,15 @@
       </c>
       <c r="D5" s="8">
         <f>Modell!$B$9/Modell!AM25</f>
-        <v>5.9925202667370909</v>
+        <v>6.1569691152821626</v>
       </c>
       <c r="E5" s="8">
         <f>Modell!$B$9/Modell!AN25</f>
-        <v>5.6300514534361259</v>
+        <v>5.7845533053374458</v>
       </c>
       <c r="F5" s="8">
         <f>Modell!$B$9/Modell!AO25</f>
-        <v>5.2221816699855612</v>
+        <v>5.36549061585416</v>
       </c>
     </row>
     <row r="6" spans="3:6" ht="62" x14ac:dyDescent="0.7">
@@ -13545,15 +13550,15 @@
       </c>
       <c r="D6" s="8">
         <f>Modell!$B$9/Modell!AM10</f>
-        <v>10.218910924168235</v>
+        <v>10.49934187142628</v>
       </c>
       <c r="E6" s="8">
         <f>Modell!$B$9/Modell!AN10</f>
-        <v>9.4481627164360962</v>
+        <v>9.7074425203290904</v>
       </c>
       <c r="F6" s="8">
         <f>Modell!$B$9/Modell!AO10</f>
-        <v>8.5062993993751803</v>
+        <v>8.7397322588969981</v>
       </c>
     </row>
     <row r="7" spans="3:6" ht="62" x14ac:dyDescent="0.7">
@@ -13562,15 +13567,15 @@
       </c>
       <c r="D7" s="8">
         <f>Modell!$B$4/Modell!AM18</f>
-        <v>14.290203590669268</v>
+        <v>14.727315700501503</v>
       </c>
       <c r="E7" s="8">
         <f>Modell!$B$4/Modell!AN18</f>
-        <v>13.168829070916805</v>
+        <v>13.571640313086025</v>
       </c>
       <c r="F7" s="8">
         <f>Modell!$B$4/Modell!AO18</f>
-        <v>11.63264462218978</v>
+        <v>11.988466692986172</v>
       </c>
     </row>
   </sheetData>
@@ -13778,7 +13783,7 @@
     <row r="6" spans="1:143" x14ac:dyDescent="0.25">
       <c r="A6" s="25">
         <f>AA24</f>
-        <v>-0.22715474536217842</v>
+        <v>-0.25009307483773013</v>
       </c>
       <c r="C6" s="24" t="s">
         <v>56</v>
@@ -15262,7 +15267,7 @@
       </c>
       <c r="AA24" s="25">
         <f>(AA23-Modell!B4)/Modell!B4</f>
-        <v>-0.22715474536217842</v>
+        <v>-0.25009307483773013</v>
       </c>
     </row>
   </sheetData>

--- a/Europris modell.xlsx
+++ b/Europris modell.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/augusthodt/Desktop/Aksjemodellering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D9E48F-B00F-4C47-BDD4-824BF4AB2803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEB8E04A-4F0B-F04D-900B-B8EC21E5A103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25300" yWindow="500" windowWidth="25900" windowHeight="26740" activeTab="1" xr2:uid="{A1D7EC49-6B45-5A4D-9144-DCA361DB0A7A}"/>
   </bookViews>
@@ -2124,7 +2124,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="3">
-        <v>87.6</v>
+        <v>81</v>
       </c>
       <c r="C4" s="23" t="s">
         <v>54</v>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="B6" s="5">
         <f>B4*B5</f>
-        <v>14626.474588799998</v>
+        <v>13524.479927999999</v>
       </c>
       <c r="C6" s="24" t="s">
         <v>56</v>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="B9" s="6">
         <f>B6-B7+B8</f>
-        <v>16253.430588799998</v>
+        <v>15151.435927999999</v>
       </c>
       <c r="C9" s="24" t="s">
         <v>73</v>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="B14" s="4">
         <f>B6/U41</f>
-        <v>3.6820329591925867</v>
+        <v>3.4046195170616382</v>
       </c>
       <c r="C14" s="24" t="s">
         <v>78</v>
@@ -5367,7 +5367,7 @@
       </c>
       <c r="AY24" s="25">
         <f>(AY23-B4)/B4</f>
-        <v>0.33258876093083967</v>
+        <v>0.44117006737705611</v>
       </c>
     </row>
     <row r="25" spans="2:51" s="24" customFormat="1" x14ac:dyDescent="0.25">
@@ -13533,15 +13533,15 @@
       </c>
       <c r="D5" s="8">
         <f>Modell!$B$9/Modell!AM25</f>
-        <v>6.1569691152821626</v>
+        <v>5.7395220382062107</v>
       </c>
       <c r="E5" s="8">
         <f>Modell!$B$9/Modell!AN25</f>
-        <v>5.7845533053374458</v>
+        <v>5.392356296664861</v>
       </c>
       <c r="F5" s="8">
         <f>Modell!$B$9/Modell!AO25</f>
-        <v>5.36549061585416</v>
+        <v>5.0017063686492547</v>
       </c>
     </row>
     <row r="6" spans="3:6" ht="62" x14ac:dyDescent="0.7">
@@ -13550,15 +13550,15 @@
       </c>
       <c r="D6" s="8">
         <f>Modell!$B$9/Modell!AM10</f>
-        <v>10.49934187142628</v>
+        <v>9.7874786976173933</v>
       </c>
       <c r="E6" s="8">
         <f>Modell!$B$9/Modell!AN10</f>
-        <v>9.7074425203290904</v>
+        <v>9.0492707104468693</v>
       </c>
       <c r="F6" s="8">
         <f>Modell!$B$9/Modell!AO10</f>
-        <v>8.7397322588969981</v>
+        <v>8.1471719231877664</v>
       </c>
     </row>
     <row r="7" spans="3:6" ht="62" x14ac:dyDescent="0.7">
@@ -13567,15 +13567,15 @@
       </c>
       <c r="D7" s="8">
         <f>Modell!$B$4/Modell!AM18</f>
-        <v>14.727315700501503</v>
+        <v>13.617723421696596</v>
       </c>
       <c r="E7" s="8">
         <f>Modell!$B$4/Modell!AN18</f>
-        <v>13.571640313086025</v>
+        <v>12.549119467579544</v>
       </c>
       <c r="F7" s="8">
         <f>Modell!$B$4/Modell!AO18</f>
-        <v>11.988466692986172</v>
+        <v>11.085226051733791</v>
       </c>
     </row>
   </sheetData>
@@ -13783,7 +13783,7 @@
     <row r="6" spans="1:143" x14ac:dyDescent="0.25">
       <c r="A6" s="25">
         <f>AA24</f>
-        <v>-0.25009307483773013</v>
+        <v>-0.18898954760228601</v>
       </c>
       <c r="C6" s="24" t="s">
         <v>56</v>
@@ -15267,7 +15267,7 @@
       </c>
       <c r="AA24" s="25">
         <f>(AA23-Modell!B4)/Modell!B4</f>
-        <v>-0.25009307483773013</v>
+        <v>-0.18898954760228601</v>
       </c>
     </row>
   </sheetData>
